--- a/output/roomself_excel/4817.xlsx
+++ b/output/roomself_excel/4817.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>290523</v>
+        <v>93175</v>
       </c>
       <c r="D2" t="n">
-        <v>6400</v>
+        <v>2484</v>
       </c>
       <c r="E2" t="n">
-        <v>956</v>
+        <v>383</v>
       </c>
       <c r="F2" t="n">
-        <v>468</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>119980</v>
+        <v>197348</v>
       </c>
       <c r="D3" t="n">
-        <v>3100</v>
+        <v>4272</v>
       </c>
       <c r="E3" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F3" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23936</v>
+        <v>119980</v>
       </c>
       <c r="D4" t="n">
-        <v>1248</v>
+        <v>3100</v>
       </c>
       <c r="E4" t="n">
-        <v>176</v>
+        <v>471</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25880</v>
+        <v>89254</v>
       </c>
       <c r="D5" t="n">
-        <v>1304</v>
+        <v>2420</v>
       </c>
       <c r="E5" t="n">
-        <v>176</v>
+        <v>387</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>58806</v>
+        <v>25880</v>
       </c>
       <c r="D6" t="n">
-        <v>2124</v>
+        <v>1304</v>
       </c>
       <c r="E6" t="n">
-        <v>567</v>
+        <v>176</v>
       </c>
       <c r="F6" t="n">
-        <v>471</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89254</v>
+        <v>47432</v>
       </c>
       <c r="D9" t="n">
-        <v>2420</v>
+        <v>1752</v>
       </c>
       <c r="E9" t="n">
-        <v>471</v>
+        <v>268</v>
       </c>
       <c r="F9" t="n">
-        <v>387</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23079</v>
+        <v>23936</v>
       </c>
       <c r="D10" t="n">
-        <v>1216</v>
+        <v>1248</v>
       </c>
       <c r="E10" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F10" t="n">
-        <v>172</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47432</v>
+        <v>58806</v>
       </c>
       <c r="D11" t="n">
-        <v>1752</v>
+        <v>2124</v>
       </c>
       <c r="E11" t="n">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="F11" t="n">
-        <v>209</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>23079</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E12" t="n">
+        <v>183</v>
+      </c>
+      <c r="F12" t="n">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/4817.xlsx
+++ b/output/roomself_excel/4817.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2484</v>
       </c>
-      <c r="E2" t="n">
-        <v>383</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>289</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>269</v>
+      </c>
+      <c r="J2" t="n">
+        <v>37</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +551,38 @@
       <c r="D3" t="n">
         <v>4272</v>
       </c>
-      <c r="E3" t="n">
-        <v>566</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>468</v>
+        <v>433</v>
+      </c>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>338</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>531</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +600,38 @@
       <c r="D4" t="n">
         <v>3100</v>
       </c>
-      <c r="E4" t="n">
-        <v>471</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>373</v>
+        <v>424</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>339</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>151</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +649,38 @@
       <c r="D5" t="n">
         <v>2420</v>
       </c>
-      <c r="E5" t="n">
-        <v>387</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>285</v>
+        <v>47</v>
+      </c>
+      <c r="G5" t="n">
+        <v>38</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>293</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>265</v>
+      </c>
+      <c r="M5" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +698,23 @@
       <c r="D6" t="n">
         <v>1304</v>
       </c>
-      <c r="E6" t="n">
-        <v>176</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +731,23 @@
       <c r="D7" t="n">
         <v>2392</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>179</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>20</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +764,31 @@
       <c r="D8" t="n">
         <v>1976</v>
       </c>
-      <c r="E8" t="n">
-        <v>380</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>166</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>151</v>
+      </c>
+      <c r="J8" t="n">
+        <v>37</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +805,38 @@
       <c r="D9" t="n">
         <v>1752</v>
       </c>
-      <c r="E9" t="n">
-        <v>268</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>209</v>
+        <v>242</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>392</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>242</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +854,23 @@
       <c r="D10" t="n">
         <v>1248</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>176</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>20</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +887,23 @@
       <c r="D11" t="n">
         <v>2124</v>
       </c>
-      <c r="E11" t="n">
-        <v>372</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>293</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +920,31 @@
       <c r="D12" t="n">
         <v>1216</v>
       </c>
-      <c r="E12" t="n">
-        <v>183</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>172</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>157</v>
+      </c>
+      <c r="J12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
